--- a/01_analyses_states/Ladakh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Ladakh/results/SoIB_summaries.xlsx
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C8">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3">

--- a/01_analyses_states/Ladakh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Ladakh/results/SoIB_summaries.xlsx
@@ -393,10 +393,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>0</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -411,6 +414,9 @@
       <c r="C3">
         <v>0</v>
       </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -424,6 +430,9 @@
       <c r="C4">
         <v>0</v>
       </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -437,6 +446,9 @@
       <c r="C5">
         <v>0</v>
       </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -450,6 +462,9 @@
       <c r="C6">
         <v>0</v>
       </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -458,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -471,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C8">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -603,7 +618,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -613,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3">
@@ -663,7 +678,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -733,16 +748,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C2">
-        <v>77.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E2">
-        <v>81.59999999999999</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3">
@@ -752,16 +767,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C3">
-        <v>22.3</v>
+        <v>20.4</v>
       </c>
       <c r="D3">
         <v>18</v>
       </c>
       <c r="E3">
-        <v>18.4</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
